--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.00846748557122654</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31863249</v>
+        <v>4184272</v>
       </c>
       <c r="L2" t="n">
-        <v>18055804</v>
+        <v>2059140</v>
       </c>
       <c r="M2" t="n">
-        <v>4512840</v>
+        <v>449501</v>
       </c>
       <c r="N2" t="n">
-        <v>245703</v>
+        <v>12068</v>
       </c>
       <c r="O2" t="n">
-        <v>2678530</v>
+        <v>264422</v>
       </c>
       <c r="P2" t="n">
-        <v>1053304</v>
+        <v>103961</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999668002128601</v>
+        <v>0.9999533891677856</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8870153427124023</v>
+        <v>0.7991405725479126</v>
       </c>
       <c r="S2" t="n">
-        <v>0.782441258430481</v>
+        <v>0.6287492513656616</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7289099097251892</v>
+        <v>0.5315908789634705</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4231902658939362</v>
+        <v>0.1048516035079956</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7712156772613525</v>
+        <v>0.5843993425369263</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8475167751312256</v>
+        <v>0.7157876491546631</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029527753233312</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>31863249</v>
+        <v>4184272</v>
       </c>
       <c r="E3" t="n">
-        <v>3449206</v>
+        <v>824490</v>
       </c>
       <c r="F3" t="n">
-        <v>74694</v>
+        <v>24523</v>
       </c>
       <c r="G3" t="n">
-        <v>8114</v>
+        <v>2067</v>
       </c>
       <c r="H3" t="n">
-        <v>4807</v>
+        <v>1545</v>
       </c>
       <c r="I3" t="n">
-        <v>433</v>
+        <v>119</v>
       </c>
       <c r="J3" t="n">
-        <v>70485866</v>
+        <v>10069324</v>
       </c>
       <c r="K3" t="n">
-        <v>75452771</v>
+        <v>10327249</v>
       </c>
       <c r="L3" t="n">
-        <v>86894928</v>
+        <v>11898283</v>
       </c>
       <c r="M3" t="n">
-        <v>106690084</v>
+        <v>15082845</v>
       </c>
       <c r="N3" t="n">
-        <v>113951387</v>
+        <v>16223337</v>
       </c>
       <c r="O3" t="n">
-        <v>110550094</v>
+        <v>15717492</v>
       </c>
       <c r="P3" t="n">
-        <v>113368960</v>
+        <v>16181214</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9000763297080994</v>
+        <v>0.8306975960731506</v>
       </c>
       <c r="S3" t="n">
-        <v>0.785149872303009</v>
+        <v>0.623626708984375</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6896635890007019</v>
+        <v>0.479683130979538</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3926730751991272</v>
+        <v>0.1346349120140076</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7508544921875</v>
+        <v>0.5180052518844604</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7781891822814941</v>
+        <v>0.5372467041015625</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03201304320695698</v>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>3823216</v>
+        <v>982059</v>
       </c>
       <c r="E4" t="n">
-        <v>18055804</v>
+        <v>2059140</v>
       </c>
       <c r="F4" t="n">
-        <v>980242</v>
+        <v>218474</v>
       </c>
       <c r="G4" t="n">
-        <v>44220</v>
+        <v>14271</v>
       </c>
       <c r="H4" t="n">
-        <v>85718</v>
+        <v>25479</v>
       </c>
       <c r="I4" t="n">
-        <v>7373</v>
+        <v>2433</v>
       </c>
       <c r="J4" t="n">
-        <v>1474</v>
+        <v>296</v>
       </c>
       <c r="K4" t="n">
-        <v>4058621</v>
+        <v>1051693</v>
       </c>
       <c r="L4" t="n">
-        <v>5020438</v>
+        <v>1215838</v>
       </c>
       <c r="M4" t="n">
-        <v>1678378</v>
+        <v>396076</v>
       </c>
       <c r="N4" t="n">
-        <v>334894</v>
+        <v>103028</v>
       </c>
       <c r="O4" t="n">
-        <v>794597</v>
+        <v>188046</v>
       </c>
       <c r="P4" t="n">
-        <v>189508</v>
+        <v>41279</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999833703041077</v>
+        <v>0.9999766945838928</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8934980630874634</v>
+        <v>0.8146135807037354</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7837931513786316</v>
+        <v>0.6261774897575378</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7087438702583313</v>
+        <v>0.504304826259613</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4073609113693237</v>
+        <v>0.117891289293766</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7608988881111145</v>
+        <v>0.5492029190063477</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8113747239112854</v>
+        <v>0.6137973070144653</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>157639</v>
+        <v>49736</v>
       </c>
       <c r="E5" t="n">
-        <v>1335679</v>
+        <v>317990</v>
       </c>
       <c r="F5" t="n">
-        <v>4512840</v>
+        <v>449501</v>
       </c>
       <c r="G5" t="n">
-        <v>118294</v>
+        <v>30267</v>
       </c>
       <c r="H5" t="n">
-        <v>385878</v>
+        <v>79926</v>
       </c>
       <c r="I5" t="n">
-        <v>33047</v>
+        <v>9601</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3537359</v>
+        <v>852786</v>
       </c>
       <c r="L5" t="n">
-        <v>4940830</v>
+        <v>1242739</v>
       </c>
       <c r="M5" t="n">
-        <v>2030698</v>
+        <v>487578</v>
       </c>
       <c r="N5" t="n">
-        <v>380016</v>
+        <v>77567</v>
       </c>
       <c r="O5" t="n">
-        <v>888779</v>
+        <v>246040</v>
       </c>
       <c r="P5" t="n">
-        <v>300228</v>
+        <v>89546</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999871850013733</v>
+        <v>0.9999819397926331</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9338974356651306</v>
+        <v>0.8839864134788513</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9133139252662659</v>
+        <v>0.8502328991889954</v>
       </c>
       <c r="T5" t="n">
-        <v>0.967722475528717</v>
+        <v>0.9461711645126343</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9937786459922791</v>
+        <v>0.9889988303184509</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9853507280349731</v>
+        <v>0.9735571146011353</v>
       </c>
       <c r="W5" t="n">
-        <v>0.99573814868927</v>
+        <v>0.9920306205749512</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="D6" t="n">
-        <v>73022</v>
+        <v>16897</v>
       </c>
       <c r="E6" t="n">
-        <v>104822</v>
+        <v>22429</v>
       </c>
       <c r="F6" t="n">
-        <v>133822</v>
+        <v>27137</v>
       </c>
       <c r="G6" t="n">
-        <v>245703</v>
+        <v>12068</v>
       </c>
       <c r="H6" t="n">
-        <v>61713</v>
+        <v>9746</v>
       </c>
       <c r="I6" t="n">
-        <v>6367</v>
+        <v>1277</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>53</v>
       </c>
       <c r="D7" t="n">
-        <v>4565</v>
+        <v>2932</v>
       </c>
       <c r="E7" t="n">
-        <v>122322</v>
+        <v>46967</v>
       </c>
       <c r="F7" t="n">
-        <v>465926</v>
+        <v>116797</v>
       </c>
       <c r="G7" t="n">
-        <v>153258</v>
+        <v>51442</v>
       </c>
       <c r="H7" t="n">
-        <v>2678530</v>
+        <v>264422</v>
       </c>
       <c r="I7" t="n">
-        <v>142288</v>
+        <v>27849</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>457</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>8409</v>
+        <v>3962</v>
       </c>
       <c r="F8" t="n">
-        <v>23694</v>
+        <v>9145</v>
       </c>
       <c r="G8" t="n">
-        <v>11008</v>
+        <v>4981</v>
       </c>
       <c r="H8" t="n">
-        <v>256481</v>
+        <v>71350</v>
       </c>
       <c r="I8" t="n">
-        <v>1053304</v>
+        <v>103961</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
